--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/ValueSet-at-ediag-list-emptyreason-vs.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/ValueSet-at-ediag-list-emptyreason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
